--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="48" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -597,19 +597,23 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: further relief; pray subpa Ã¦ na.)</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: day of â€” -------he and C. D., the defendant hereinafter</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: - d</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,19 +668,15 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” except t</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: named, carried on the business of -----â€” in co-partner-</t>
-        </is>
-      </c>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: ； and</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: 9.</t>
+          <t>L19: isolated marker/symbol line :: - d</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: day of â€” -------he and C. D., the defendant hereinafter</t>
+          <t>L16: punctuation artifact: double/multiple hyphen :: day of — -------he and C. D., the defendant hereinafter</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -730,16 +730,12 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”except tl</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 130</t>
+          <t>L22: isolated marker/symbol line :: 9.</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -754,7 +750,7 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: named, carried on the business of -----â€” in co-partner-</t>
+          <t>L17: punctuation artifact: double/multiple hyphen :: named, carried on the business of -----— in co-partner-</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -789,16 +785,12 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: der an indenture, dated the ---------day of - :â€”,</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 4</t>
+          <t>L27: isolated marker/symbol line :: 130</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -845,7 +837,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 10.</t>
+          <t>L58: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -892,7 +884,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: O</t>
+          <t>L59: symbol-only separator/garbage line :: 10.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -939,14 +931,14 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: *;</t>
+          <t>L123: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: der an indenture, dated the ---------day of - :â€”,</t>
+          <t>L114: punctuation artifact: double/multiple hyphen :: der an indenture, dated the ---------day of - :—,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -984,7 +976,11 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L133: isolated marker/symbol line :: *;</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1053,7 +1049,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1087,7 +1083,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
